--- a/reports/Debug-purgatory-20260104/Week Total (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260104/Week Total (Prior Year)_Revenue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
   <si>
     <t>DepartmentTitle</t>
   </si>
@@ -64,25 +64,64 @@
     <t>Village Market Deli</t>
   </si>
   <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Purgatory</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>Accounting/Mgmt Services</t>
+  </si>
+  <si>
     <t>Guest Services</t>
   </si>
   <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
     <t>Grounds Maintenance</t>
   </si>
   <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Commercial Tenants</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>General Administration</t>
+  </si>
+  <si>
+    <t>DMC Dgo Mtn Club</t>
+  </si>
+  <si>
     <t>account</t>
   </si>
   <si>
+    <t>T103</t>
+  </si>
+  <si>
+    <t>T105</t>
+  </si>
+  <si>
+    <t>T100</t>
+  </si>
+  <si>
     <t>T104</t>
   </si>
   <si>
-    <t>T105</t>
-  </si>
-  <si>
-    <t>T100</t>
-  </si>
-  <si>
-    <t>T103</t>
+    <t>T101</t>
   </si>
   <si>
     <t>department</t>
@@ -118,7 +157,7 @@
     <t>D5202</t>
   </si>
   <si>
-    <t xml:space="preserve">D5205                    </t>
+    <t>D5205</t>
   </si>
   <si>
     <t>D5206</t>
@@ -133,10 +172,46 @@
     <t>D5209</t>
   </si>
   <si>
-    <t xml:space="preserve">D6720                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">D6780                    </t>
+    <t>D5810</t>
+  </si>
+  <si>
+    <t>D6212</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6710</t>
+  </si>
+  <si>
+    <t>D6720</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D6750</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D6800</t>
+  </si>
+  <si>
+    <t>D7010</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8810</t>
   </si>
   <si>
     <t>revenue</t>
@@ -502,13 +577,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -516,27 +590,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
       <c r="D2" s="2">
-        <v>631.6200</v>
+        <v>15.00</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -544,13 +612,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2">
-        <v>17835.0000</v>
+        <v>17295.00</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -558,13 +626,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2">
-        <v>1591709.3400</v>
+        <v>17951.00</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -572,205 +640,377 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2">
-        <v>300.0000</v>
+        <v>1591482.34</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2">
-        <v>395139.7000</v>
+        <v>631.62</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D7" s="2">
-        <v>11440.0000</v>
+        <v>661259.53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2">
-        <v>302488.2900</v>
+        <v>412306.52</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D9" s="2">
-        <v>25679.0900</v>
+        <v>11440.00</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2">
-        <v>112964.5000</v>
+        <v>313498.29</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2">
-        <v>37412.4000</v>
+        <v>36264.53</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D12" s="2">
-        <v>46539.1700</v>
+        <v>195947.14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2">
-        <v>60674.5300</v>
+        <v>63969.84</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2">
-        <v>95563.3000</v>
+        <v>65747.09</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2">
-        <v>13385.8100</v>
+        <v>76600.65</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2">
-        <v>5870.0000</v>
+        <v>145200.78</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D17" s="2">
-        <v>50924.3300</v>
+        <v>13627.15</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D18" s="2">
-        <v>152857.3000</v>
+        <v>5871.44</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D19" s="2">
-        <v>36088.1600</v>
+        <v>62368.44</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2">
-        <v>13905.0000</v>
+        <v>228933.08</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2">
-        <v>960.0000</v>
+        <v>46171.39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="2">
+        <v>12000.00</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="2">
+        <v>867005.22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="2">
+        <v>27105.00</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="2">
+        <v>26036.10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="2">
+        <v>136024.00</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="2">
+        <v>16451.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="2">
+        <v>20849.82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="2">
+        <v>61630.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="2">
+        <v>50184.04</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="2">
+        <v>42829.54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="2">
+        <v>17508.17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="2">
+        <v>4000.00</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="2">
+        <v>29562.99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="2">
+        <v>682.07</v>
       </c>
     </row>
   </sheetData>
